--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\INDIND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF97F263-41E9-4E88-B424-C4CAC3EFD538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61D35E6-C619-4E87-97B7-4E659400F6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3519,6 +3519,7 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">

--- a/VT_REG_PRI_V01.xlsx
+++ b/VT_REG_PRI_V01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\INDIND\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D61D35E6-C619-4E87-97B7-4E659400F6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45804E57-1A84-486F-A70E-D0635C7D3F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
